--- a/internal_doc/03.开发设计/OM/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM/OM_web接口.xlsx
@@ -1758,25 +1758,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{
-    OM_BSON_BUSINESS_TYPE:type,
-    OM_BSON_FIELD_CLUSTER_NAME:"c1",
-    OM_BSON_BUSINESS_NAME:"b1",
-    OM_BSON_DEPLOY_MOD:"mode",
-    OM_BSON_FIELD_CONFIG:
-    [
-    {
-        OM_BSON_FIELD_HOST_NAME:"host",
-        OM_BSON_FIELD_HOST_USER:"",
-        OM_BSON_FIELD_HOST_PASSWD:"",
-        OM_BSON_FIELD_HOST_SSHPORT:"",
-        svcname:"",
-    }
-    ]
-}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">{
     OM_BSON_BUSINESS_TYPE:type,
@@ -2158,6 +2139,27 @@
         OM_BSON_FIELD_HOST_SSHPORT:""
     }
     , ...
+    ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    OM_BSON_BUSINESS_TYPE:type,
+    OM_BSON_FIELD_CLUSTER_NAME:"c1",
+    OM_BSON_BUSINESS_NAME:"b1",
+    OM_BSON_DEPLOY_MOD:"mode",
+    OM_BUSINESSAUTH_USER:"sdb",
+    OM_BUSINESSAUTH_USER:"sdb",
+    OM_BSON_FIELD_CONFIG:
+    [
+    {
+        OM_BSON_FIELD_HOST_NAME:"host",
+        OM_BSON_FIELD_HOST_USER:"",
+        OM_BSON_FIELD_HOST_PASSWD:"",
+        OM_BSON_FIELD_HOST_SSHPORT:"",
+        svcname:"",
+    }
     ]
 }</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5335,7 +5337,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="24" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>218</v>
@@ -5885,7 +5887,7 @@
         <v>44</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C3" s="43" t="s">
         <v>340</v>
@@ -5896,18 +5898,18 @@
         <v>191</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C4" s="43" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="204">
+    <row r="5" spans="1:3" ht="216">
       <c r="A5" s="44" t="s">
         <v>306</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>343</v>
+        <v>392</v>
       </c>
       <c r="C5" s="43" t="s">
         <v>341</v>
@@ -5999,45 +6001,45 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>218</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>186</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" ht="156">
       <c r="A3" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6049,86 +6051,86 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" ht="144">
       <c r="A6" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" ht="132">
       <c r="A7" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" ht="132">
       <c r="A8" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>187</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="52" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>367</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="52" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="52" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E11" s="4"/>
     </row>
@@ -6141,27 +6143,27 @@
     </row>
     <row r="13" spans="1:5" ht="409.5">
       <c r="A13" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>372</v>
-      </c>
       <c r="D13" s="52" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" ht="24">
       <c r="A14" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="52" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E14" s="4"/>
     </row>
@@ -6174,29 +6176,29 @@
     </row>
     <row r="16" spans="1:5" ht="168">
       <c r="A16" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>377</v>
-      </c>
       <c r="D16" s="52" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5" ht="24">
       <c r="A17" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D17" s="52" t="s">
         <v>380</v>
-      </c>
-      <c r="D17" s="52" t="s">
-        <v>381</v>
       </c>
       <c r="E17" s="4"/>
     </row>
@@ -6209,29 +6211,29 @@
     </row>
     <row r="19" spans="1:5" ht="168">
       <c r="A19" s="9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>377</v>
-      </c>
       <c r="D19" s="52" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" ht="24">
       <c r="A20" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D20" s="52" t="s">
         <v>380</v>
-      </c>
-      <c r="D20" s="52" t="s">
-        <v>381</v>
       </c>
       <c r="E20" s="4"/>
     </row>
@@ -6244,29 +6246,29 @@
     </row>
     <row r="22" spans="1:5" ht="192">
       <c r="A22" s="9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>377</v>
-      </c>
       <c r="D22" s="52" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" ht="24">
       <c r="A23" s="9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D23" s="52" t="s">
         <v>380</v>
-      </c>
-      <c r="D23" s="52" t="s">
-        <v>381</v>
       </c>
       <c r="E23" s="4"/>
     </row>
@@ -6279,29 +6281,29 @@
     </row>
     <row r="25" spans="1:5" ht="192">
       <c r="A25" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>377</v>
-      </c>
       <c r="D25" s="52" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:5" ht="24">
       <c r="A26" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D26" s="52" t="s">
         <v>380</v>
-      </c>
-      <c r="D26" s="52" t="s">
-        <v>381</v>
       </c>
       <c r="E26" s="4"/>
     </row>

--- a/internal_doc/03.开发设计/OM/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="6"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -15,6 +15,7 @@
     <sheet name="Sheet3" sheetId="7" r:id="rId6"/>
     <sheet name="Sheet1" sheetId="8" r:id="rId7"/>
     <sheet name="与agent消息(new)" sheetId="9" r:id="rId8"/>
+    <sheet name="zookeeper" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -282,7 +283,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="397">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2161,6 +2162,136 @@
         svcname:"",
     }
     ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADD_BUSINESS的task表结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "AgentHost: agent主机名,
+  "AgentService": agent端口号,
+  "CreateTime": 任务创建时间,
+  "EndTime": 任务结束时间,
+  "Info": {
+    "SdbUser": sdbadmin用户名,
+    "SdbPasswd"：sdbadmin密码,
+    "SdbUserGroup": 所属的用户组,
+    "Config": [
+      {
+        "HostName": 节点主机名,
+        "datagroupname": 数据组,
+        "dbpath": 数据目录,
+        "svcname": 服务端口,
+        "role": 角色,
+        "diaglevel": 日志级别,
+        "hjbuf": buf大小,
+        "logbuffsize": 日志缓充大小,
+        "logfilenum": 日志文件数目,
+        "logfilesz": "64",
+        "maxprefpool": "200",
+        "maxreplsync": "10",
+        "numpagecleaners": "1",
+        "numpreload": "0",
+        "pagecleaninterval": "10000",
+        "preferedinstance": "A",
+        "sortbuf": "512",
+        "syncstrategy": "keepnormal",
+        "transactionon": "false",
+        "weight": "10",
+        "User": 主机的超级用户名root,
+        "Passwd": 主机的超级用户密码,
+        "SshPort": "22"
+      }
+    ],
+    "ClusterName": "c1",
+    "BusinessType": "sequoiadb",
+    "BusinessName": "myModule",
+    "DeployMod": "distribution"
+  },
+  "Progress": 100,
+  "ResultInfo": [
+    {
+      "errno": 0,
+      "detail": "",
+      "HostName": "r720-77",
+      "svcname": "11810",
+      "role": "coord",
+      "datagroupname": "",
+      "Status": 4,
+      "StatusDesc": "FINISH",
+      "Flow": [处理流程]"
+      ]
+    }
+  ],
+  "Status": 4,
+  "StatusDesc": "FINISH",
+  "TaskID": 11,
+  "TaskName": "ADD_BUSINESS",
+  "Type": 2,
+  "TypeDesc": "ADD_BUSINESS",
+  "detail": "",
+  "errno": 0
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加zookeeper业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "AgentHost: agent主机名,
+  "AgentService": agent端口号，
+  "CreateTime": 任务创建时间,
+  "EndTime": 任务结束时间,
+  "Status": 4,
+  "StatusDesc": "FINISH",
+  "TaskID": 11,
+  "TaskName": "ADD_BUSINESS",
+  "Type": 2,
+  "TypeDesc": "ADD_BUSINESS",
+  "detail": "",
+  "errno": 0
+  "Progress": 100,
+  "Info": {
+    "ClusterName": "c1",
+    "BusinessType": zookeeper",
+    "BusinessName": "myZookeeper",
+    "DeployMod": "distribution"
+    "PacketPath":安装包路径
+    "Config": [
+      {
+        "HostName": 节点主机名,
+        "User": 主机的超级用户名root,
+        "Passwd": 主机的超级用户密码,
+        "SshPort": "22"
+        "zooid": zookeeper ID
+        "installpath"
+        "datapath"
+        "dataport"
+        "electport"
+        "clientport"
+        "synclimit"
+        "initlimit"
+        "ticktime"
+      }
+    ],
+  },
+  "ResultInfo": [
+    {
+      "errno": 0,
+      "detail": "",
+      "HostName": "r720-77",
+      "zooid":
+      "Status": 4,
+      "StatusDesc": "FINISH",
+      "Flow": [处理流程]"
+      ]
+    }
+  ]
 }</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2423,7 +2554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2567,6 +2698,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5989,7 +6123,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22.375" style="23" bestFit="1" customWidth="1"/>
@@ -6244,82 +6378,86 @@
       <c r="D21" s="57"/>
       <c r="E21" s="56"/>
     </row>
-    <row r="22" spans="1:5" ht="192">
+    <row r="22" spans="1:5" ht="409.5">
       <c r="A22" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="52" t="s">
+        <v>394</v>
+      </c>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" ht="192">
+      <c r="A23" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B23" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C23" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="D22" s="52" t="s">
+      <c r="D23" s="52" t="s">
         <v>385</v>
       </c>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" ht="24">
-      <c r="A23" s="9" t="s">
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" ht="24">
+      <c r="A24" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4" t="s">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="D23" s="52" t="s">
+      <c r="D24" s="52" t="s">
         <v>380</v>
       </c>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="55"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="56"/>
-    </row>
-    <row r="25" spans="1:5" ht="192">
-      <c r="A25" s="9" t="s">
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="55"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="56"/>
+    </row>
+    <row r="26" spans="1:5" ht="192">
+      <c r="A26" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C26" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="D25" s="52" t="s">
+      <c r="D26" s="52" t="s">
         <v>386</v>
       </c>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5" ht="24">
-      <c r="A26" s="9" t="s">
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" ht="24">
+      <c r="A27" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4" t="s">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="D26" s="52" t="s">
+      <c r="D27" s="52" t="s">
         <v>380</v>
       </c>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="55"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="56"/>
+      <c r="E27" s="4"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="9"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="4"/>
+      <c r="A28" s="55"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="56"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="9"/>
@@ -6332,7 +6470,7 @@
       <c r="A30" s="9"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="9"/>
+      <c r="D30" s="52"/>
       <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:5">
@@ -6342,6 +6480,47 @@
       <c r="D31" s="9"/>
       <c r="E31" s="4"/>
     </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="9"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="55"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="56"/>
+    </row>
+    <row r="2" spans="1:5" ht="243" customHeight="1">
+      <c r="A2" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="64" t="s">
+        <v>396</v>
+      </c>
+      <c r="E2" s="4"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/03.开发设计/OM/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM/OM_web接口.xlsx
@@ -2681,6 +2681,9 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2698,9 +2701,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3112,7 +3112,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="59" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -3130,7 +3130,7 @@
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="13.5">
-      <c r="A4" s="59"/>
+      <c r="A4" s="60"/>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
@@ -3146,7 +3146,7 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="13.5">
-      <c r="A5" s="59"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
@@ -3162,7 +3162,7 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="60"/>
+      <c r="A6" s="61"/>
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
@@ -3178,7 +3178,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="24">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="62" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -3196,7 +3196,7 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="36">
-      <c r="A8" s="62"/>
+      <c r="A8" s="63"/>
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
@@ -3214,7 +3214,7 @@
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="72">
-      <c r="A9" s="62"/>
+      <c r="A9" s="63"/>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
@@ -3232,7 +3232,7 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="24">
-      <c r="A10" s="63"/>
+      <c r="A10" s="64"/>
       <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
@@ -3270,7 +3270,7 @@
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="24">
-      <c r="A12" s="61" t="s">
+      <c r="A12" s="62" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -3288,7 +3288,7 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="62"/>
+      <c r="A13" s="63"/>
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
@@ -3304,7 +3304,7 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="24">
-      <c r="A14" s="62"/>
+      <c r="A14" s="63"/>
       <c r="B14" s="4" t="s">
         <v>33</v>
       </c>
@@ -3322,7 +3322,7 @@
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="62"/>
+      <c r="A15" s="63"/>
       <c r="B15" s="4" t="s">
         <v>35</v>
       </c>
@@ -3338,7 +3338,7 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="62"/>
+      <c r="A16" s="63"/>
       <c r="B16" s="4" t="s">
         <v>57</v>
       </c>
@@ -3350,7 +3350,7 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="48">
-      <c r="A17" s="62"/>
+      <c r="A17" s="63"/>
       <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
@@ -3368,7 +3368,7 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="62"/>
+      <c r="A18" s="63"/>
       <c r="B18" s="4" t="s">
         <v>38</v>
       </c>
@@ -3384,7 +3384,7 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="62"/>
+      <c r="A19" s="63"/>
       <c r="B19" s="4" t="s">
         <v>41</v>
       </c>
@@ -3400,7 +3400,7 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="62"/>
+      <c r="A20" s="63"/>
       <c r="B20" s="4" t="s">
         <v>40</v>
       </c>
@@ -3416,7 +3416,7 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="24">
-      <c r="A21" s="62"/>
+      <c r="A21" s="63"/>
       <c r="B21" s="4" t="s">
         <v>44</v>
       </c>
@@ -3434,7 +3434,7 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="24">
-      <c r="A22" s="62"/>
+      <c r="A22" s="63"/>
       <c r="B22" s="4" t="s">
         <v>47</v>
       </c>
@@ -3450,7 +3450,7 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="24">
-      <c r="A23" s="62"/>
+      <c r="A23" s="63"/>
       <c r="B23" s="4" t="s">
         <v>49</v>
       </c>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="9"/>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="58" t="s">
         <v>396</v>
       </c>
       <c r="E2" s="4"/>

--- a/internal_doc/03.开发设计/OM/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM/OM_web接口.xlsx
@@ -283,7 +283,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="399">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2262,6 +2262,63 @@
     "BusinessName": "myZookeeper",
     "DeployMod": "distribution"
     "PacketPath":安装包路径
+    "Config": [
+      {
+        "HostName": 节点主机名,
+        "User": 主机的超级用户名root,
+        "Passwd": 主机的超级用户密码,
+        "SshPort": "22"
+        "zooid": zookeeper ID
+        "installpath"
+        "datapath"
+        "dataport"
+        "electport"
+        "clientport"
+        "synclimit"
+        "initlimit"
+        "ticktime"
+      }
+    ],
+  },
+  "ResultInfo": [
+    {
+      "errno": 0,
+      "detail": "",
+      "HostName": "r720-77",
+      "zooid":
+      "Status": 4,
+      "StatusDesc": "FINISH",
+      "Flow": [处理流程]"
+      ]
+    }
+  ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卸载zookeeper业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "AgentHost: agent主机名,
+  "AgentService": agent端口号，
+  "CreateTime": 任务创建时间,
+  "EndTime": 任务结束时间,
+  "Status": 4,
+  "StatusDesc": "FINISH",
+  "TaskID": 11,
+  "TaskName": "REMOVE_BUSINESS",
+  "Type": 3,
+  "TypeDesc": "REMOVE_BUSINESS",
+  "detail": "",
+  "errno": 0
+  "Progress": 100,
+  "Info": {
+    "ClusterName": "c1",
+    "BusinessType": zookeeper",
+    "BusinessName": "myZookeeper",
+    "DeployMod": "distribution"
     "Config": [
       {
         "HostName": 节点主机名,
@@ -6496,7 +6553,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
@@ -6521,6 +6578,59 @@
       </c>
       <c r="E2" s="4"/>
     </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="9"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" ht="200.1" customHeight="1">
+      <c r="A4" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="58" t="s">
+        <v>398</v>
+      </c>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="9"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="9"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="9"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="9"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="9"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="4"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/03.开发设计/OM/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM/OM_web接口.xlsx
@@ -2242,6 +2242,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>卸载zookeeper业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>{
   "AgentHost: agent主机名,
   "AgentService": agent端口号，
@@ -2261,6 +2265,9 @@
     "BusinessType": zookeeper",
     "BusinessName": "myZookeeper",
     "DeployMod": "distribution"
+    "SdbUser": sdbadmin用户名,
+    "SdbPasswd"：sdbadmin密码,
+    "SdbUserGroup": 所属的用户组,
     "PacketPath":安装包路径
     "Config": [
       {
@@ -2296,10 +2303,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>卸载zookeeper业务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{
   "AgentHost: agent主机名,
   "AgentService": agent端口号，
@@ -2318,6 +2321,9 @@
     "ClusterName": "c1",
     "BusinessType": zookeeper",
     "BusinessName": "myZookeeper",
+    "SdbUser": sdbadmin用户名,
+    "SdbPasswd"：sdbadmin密码,
+    "SdbUserGroup": 所属的用户组,
     "DeployMod": "distribution"
     "Config": [
       {
@@ -6574,7 +6580,7 @@
       <c r="B2" s="4"/>
       <c r="C2" s="9"/>
       <c r="D2" s="58" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E2" s="4"/>
     </row>
@@ -6587,7 +6593,7 @@
     </row>
     <row r="4" spans="1:5" ht="200.1" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9"/>

--- a/internal_doc/03.开发设计/OM/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="8"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -2044,22 +2044,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>agent更新ADD_BUSINESS任务进度请求(agent-&gt;om)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>agent更新ADD_BUSINESS任务进度响应(om-&gt;agent)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>agent更新REMOVE_BUSINESS任务进度请求(agent-&gt;om)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>agent更新REMOVE_BUSINESS任务进度响应(om-&gt;agent)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>以内部的Query命令发，命令字为update task
 ResultInfo不同任务类型格式不一样：
 task为添加业务时，ResultInfo:
@@ -2356,6 +2340,22 @@
     }
   ]
 }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新ADD_BUSINESS任务Sequoiadb进度请求(agent-&gt;om)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新ADD_BUSINESS任务Sequoiadb进度响应(om-&gt;agent)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新REMOVE_BUSINESS任务Sequoiadb进度请求(agent-&gt;om)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新REMOVE_BUSINESS任务Sequoiadb进度响应(om-&gt;agent)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6084,7 +6084,7 @@
         <v>44</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C3" s="43" t="s">
         <v>340</v>
@@ -6106,7 +6106,7 @@
         <v>306</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C5" s="43" t="s">
         <v>341</v>
@@ -6343,7 +6343,7 @@
         <v>370</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>371</v>
@@ -6382,7 +6382,7 @@
         <v>376</v>
       </c>
       <c r="D16" s="52" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E16" s="4"/>
     </row>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="19" spans="1:5" ht="168">
       <c r="A19" s="9" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>375</v>
@@ -6417,13 +6417,13 @@
         <v>376</v>
       </c>
       <c r="D19" s="52" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" ht="24">
       <c r="A20" s="9" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4" t="s">
@@ -6443,18 +6443,18 @@
     </row>
     <row r="22" spans="1:5" ht="409.5">
       <c r="A22" s="9" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9"/>
       <c r="D22" s="52" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" ht="192">
       <c r="A23" s="9" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>375</v>
@@ -6463,13 +6463,13 @@
         <v>376</v>
       </c>
       <c r="D23" s="52" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E23" s="4"/>
     </row>
-    <row r="24" spans="1:5" ht="24">
+    <row r="24" spans="1:5" ht="36">
       <c r="A24" s="9" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4" t="s">
@@ -6489,7 +6489,7 @@
     </row>
     <row r="26" spans="1:5" ht="192">
       <c r="A26" s="9" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>375</v>
@@ -6498,13 +6498,13 @@
         <v>376</v>
       </c>
       <c r="D26" s="52" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E26" s="4"/>
     </row>
-    <row r="27" spans="1:5" ht="24">
+    <row r="27" spans="1:5" ht="36">
       <c r="A27" s="9" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4" t="s">
@@ -6575,12 +6575,12 @@
     </row>
     <row r="2" spans="1:5" ht="243" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="9"/>
       <c r="D2" s="58" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E2" s="4"/>
     </row>
@@ -6593,12 +6593,12 @@
     </row>
     <row r="4" spans="1:5" ht="200.1" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9"/>
       <c r="D4" s="58" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E4" s="4"/>
     </row>

--- a/internal_doc/03.开发设计/OM/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM/OM_web接口.xlsx
@@ -283,7 +283,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="409">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1979,55 +1979,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">agent通过TaskID向OM发送查询请求（与查表请求格式一样），表结构参见OM架构设计--Task表结构;这里只描述不同的两个字段：
-Info：
-{
-    OM_BSON_FIELD_CLUSTER_NAME:"c1",
-    OM_BSON_FIELD_SDB_USER:"usr",
-    OM_BSON_FIELD_SDB_PASSWD:"passwd",
-    OM_BSON_FIELD_SDB_USERGROUP:"usr_group",
-    OM_BSON_FIELD_PATCKET_PATH:"path",
-    OM_BSON_FIELD_HOST_INFO:
-    [
-    {
-        OM_HOST_FIELD_NAME:"host",
-        OM_HOST_FIELD_CLUSTERNAME:"c1",
-        OM_HOST_FIELD_IP:"ip"...
-    }
-    , ...
-    ]
-}
-ResultInfo:
-{
-  [
-    {
-    OM_HOST_FIELD_IP:"ip",
-    OM_HOST_FIELD_NAME:"host",
-    OM_TASKINFO_FIELD_STATUS:1,
-    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
-    OM_REST_RES_RETCODE:0,
-    OM_REST_RES_DETAIL:"detail",
-    OM_TASKINFO_FIELD_FLOW:null
-    }
-  ]
-}
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update task</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{
-  TaskID:
-  Status:
-  Progress:
-  ResultInfo:
-}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>agent更新ADD_HOST任务进度请求(agent-&gt;om)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2041,61 +1996,6 @@
   </si>
   <si>
     <t>flag==0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>以内部的Query命令发，命令字为update task
-ResultInfo不同任务类型格式不一样：
-task为添加业务时，ResultInfo:
-[
-{
-    OM_BSON_FIELD_HOST_NAME:"host1",
-    OM_CONF_DETAIL_SVCNAME:"",
-    OM_CONF_DETAIL_ROLE:"",
-    OM_CONF_DETAIL_DATAGROUPNAME:"",
-    OM_TASKINFO_FIELD_STATUS:1,
-    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
-    OM_REST_RES_RETCODE:0,
-    OM_REST_RES_DETAIL:"detail",
-    OM_TASKINFO_FIELD_FLOW:null
-}
-]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>以内部的Query命令发，命令字为update task
-ResultInfo不同任务类型格式不一样：
-task为删除业务时，ResultInfo:
-[
-{
-    OM_BSON_FIELD_HOST_NAME:"host1",
-    OM_CONF_DETAIL_SVCNAME:"",
-    OM_CONF_DETAIL_ROLE:"",
-    OM_CONF_DETAIL_DATAGROUPNAME:"",
-    OM_TASKINFO_FIELD_STATUS:1,
-    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
-    OM_REST_RES_RETCODE:0,
-    OM_REST_RES_DETAIL:"detail",
-    OM_TASKINFO_FIELD_FLOW:null
-}
-]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>以内部的Query命令发，命令字为update task
-ResultInfo不同任务类型格式不一样：
-task为添加机器时，ResultInfo:
-[
-{
-    OM_HOST_FIELD_IP:"ip",
-    OM_HOST_FIELD_NAME:"host",
-    OM_TASKINFO_FIELD_STATUS:1,
-    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
-    OM_REST_RES_RETCODE:0,
-    OM_REST_RES_DETAIL:"detail",
-    OM_TASKINFO_FIELD_FLOW:null
-}
-]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2147,10 +2047,6 @@
     }
     ]
 }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADD_BUSINESS的task表结构</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2356,6 +2252,231 @@
   </si>
   <si>
     <t>agent更新REMOVE_BUSINESS任务Sequoiadb进度响应(om-&gt;agent)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  TaskID:
+  Status:
+  Progress:
+  errono:
+  ResultInfo:
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  TaskID:
+  Status:
+  errno:
+  Progress:
+  ResultInfo:
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">agent通过TaskID向OM发送查询请求（与查表请求格式一样），表结构参见OM架构设计--Task表结构;这里只描述不同的两个字段：
+Info：
+{
+    OM_BSON_FIELD_CLUSTER_NAME:"c1",
+    OM_BSON_FIELD_SDB_USER:"usr",
+    OM_BSON_FIELD_SDB_PASSWD:"passwd",
+    OM_BSON_FIELD_SDB_USERGROUP:"usr_group",
+    OM_BSON_FIELD_PATCKET_PATH:"path",
+    OM_BSON_FIELD_HOST_INFO:
+    [
+    {
+        OM_HOST_FIELD_NAME:"host",
+        OM_HOST_FIELD_CLUSTERNAME:"c1",
+        OM_HOST_FIELD_IP:"ip"...
+    }
+    , ...
+    ]
+}
+ResultInfo:
+{
+  [
+    {
+    OM_HOST_FIELD_IP:"ip",
+    OM_HOST_FIELD_NAME:"host",
+    OM_TASKINFO_FIELD_STATUS:1,
+    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
+    OM_REST_RES_RETCODE:0,
+    OM_REST_RES_DETAIL:"detail",
+    OM_TASKINFO_FIELD_FLOW:[]
+    }
+  ]
+}
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以内部的Query命令发，命令字为update task
+ResultInfo不同任务类型格式不一样：
+task为添加机器时，ResultInfo:
+[
+{
+    OM_HOST_FIELD_IP:"ip",
+    OM_HOST_FIELD_NAME:"host",
+    OM_TASKINFO_FIELD_STATUS:1,
+    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
+    OM_REST_RES_RETCODE:0,
+    OM_REST_RES_DETAIL:"detail",
+    OM_TASKINFO_FIELD_FLOW:[]
+}
+]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以内部的Query命令发，命令字为update task
+ResultInfo不同任务类型格式不一样：
+task为添加业务时，ResultInfo:
+[
+{
+    OM_BSON_FIELD_HOST_NAME:"host1",
+    OM_CONF_DETAIL_SVCNAME:"",
+    OM_CONF_DETAIL_ROLE:"",
+    OM_CONF_DETAIL_DATAGROUPNAME:"",
+    OM_TASKINFO_FIELD_STATUS:1,
+    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
+    OM_REST_RES_RETCODE:0,
+    OM_REST_RES_DETAIL:"detail",
+    OM_TASKINFO_FIELD_FLOW:[]
+}
+]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以内部的Query命令发，命令字为update task
+ResultInfo不同任务类型格式不一样：
+task为删除业务时，ResultInfo:
+[
+{
+    OM_BSON_FIELD_HOST_NAME:"host1",
+    OM_CONF_DETAIL_SVCNAME:"",
+    OM_CONF_DETAIL_ROLE:"",
+    OM_CONF_DETAIL_DATAGROUPNAME:"",
+    OM_TASKINFO_FIELD_STATUS:1,
+    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
+    OM_REST_RES_RETCODE:0,
+    OM_REST_RES_DETAIL:"detail",
+    OM_TASKINFO_FIELD_FLOW:[]
+}
+]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADD_BUSINESS的SequoiaDB业务的task表结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADD_BUSINESS的zookeeper业务的task表结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  {
+  "AgentHost": "suse-lyb",
+  "AgentService": "11790",
+  "CreateTime": {
+    "$timestamp": "2015-06-10-10.27.02.000000"
+  },
+  "EndTime": {
+    "$timestamp": "2015-06-10-10.28.43.000000"
+  },
+  "Info": {
+    "SdbUser": "root",
+    "SdbPasswd": "sequoiadb",
+    "SdbUserGroup": "root",
+    "Config": [
+      {
+        "HostName": "suse-lyb",
+        "zooid": "1",
+        "installpath": "/opt/zookeeper/zoo1/database/11870",
+        "datapath": "/home/mount/zookeeper/zoo1/database/11870",
+        "dataport": "11870",
+        "electport": "11871",
+        "clientport": "11872",
+        "initlimit": "5",
+        "synclimit": "2",
+        "ticktime": "2000",
+        "User": "root",
+        "Passwd": "sequoiadb",
+        "SshPort": "22"
+      }
+    ],
+    "ClusterName": "c1",
+    "BusinessType": "zookeeper",
+    "BusinessName": "zoo1",
+    "DeployMod": "distribution",
+    "InstallPacket": "/home/mount/sequoiadb/trunk/bin/../packet/zookeeper-3.4.5.tar.gz"
+  },
+  "Progress": 100,
+  "ResultInfo": [
+    {
+      "HostName": "suse-lyb",
+      "zooid": "1",
+      "Status": 4,
+      "StatusDesc": "FINISH",
+      "errno": 0,
+      "detail": "",
+      "Flow": ""
+    }
+  ],
+  "Status": 4,
+  "StatusDesc": "INIT",
+  "TaskID": 2,
+  "TaskName": "ADD_BUSINESS",
+  "Type": 2,
+  "TypeDesc": "ADD_BUSINESS",
+  "_id": {
+    "$oid": "5577a07600c99eaf9e720e07"
+  },
+  "detail": "",
+  "errno": 0
+}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以内部的Query命令发，命令字为update task
+ResultInfo不同任务类型格式不一样：
+task为添加业务时，ResultInfo:
+[
+{
+    "HostName": "suse-lyb",
+    "zooid": "1",
+    "Status": 4,
+    "StatusDesc": "FINISH",
+    "errno": 0,
+    "detail": "",
+    "Flow": ""
+}
+]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机相关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SequoiaDB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新ADD_BUSINESS任务zookeeper进度请求(agent-&gt;om)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新ADD_BUSINESS任务zookeeper进度响应(om-&gt;agent)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新REMOVE_BUSINESS任务zookeeper进度请求(agent-&gt;om)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新REMOVE_BUSINESS任务zookeeper进度响应(om-&gt;agent)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2617,7 +2738,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2764,6 +2885,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6084,7 +6223,7 @@
         <v>44</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C3" s="43" t="s">
         <v>340</v>
@@ -6106,7 +6245,7 @@
         <v>306</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C5" s="43" t="s">
         <v>341</v>
@@ -6186,371 +6325,460 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.375" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
-    <col min="4" max="4" width="46.5" style="23" customWidth="1"/>
-    <col min="5" max="5" width="28.375" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="23" customWidth="1"/>
+    <col min="2" max="2" width="22.375" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37" customWidth="1"/>
+    <col min="5" max="5" width="46.5" style="23" customWidth="1"/>
+    <col min="6" max="6" width="28.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" s="65" t="s">
+        <v>403</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5" ht="156">
-      <c r="A3" s="9" t="s">
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" ht="156">
+      <c r="A3" s="66"/>
+      <c r="B3" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="9"/>
+      <c r="F3" s="9" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="53"/>
+    <row r="4" spans="1:6">
+      <c r="A4" s="66"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54"/>
       <c r="D4" s="53"/>
       <c r="E4" s="53"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="11" t="s">
+      <c r="F4" s="53"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="66"/>
+      <c r="B5" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="18"/>
+      <c r="D5" s="18" t="s">
         <v>355</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" ht="144">
-      <c r="A6" s="9" t="s">
+      <c r="F5" s="18"/>
+    </row>
+    <row r="6" spans="1:6" ht="144">
+      <c r="A6" s="66"/>
+      <c r="B6" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" ht="132">
-      <c r="A7" s="9" t="s">
+      <c r="E6" s="9"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" ht="132">
+      <c r="A7" s="66"/>
+      <c r="B7" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" ht="132">
-      <c r="A8" s="9" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" ht="132">
+      <c r="A8" s="66"/>
+      <c r="B8" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="D8" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="9" t="s">
+      <c r="E8" s="9"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="66"/>
+      <c r="B9" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="52" t="s">
+      <c r="D9" s="4"/>
+      <c r="E9" s="52" t="s">
         <v>364</v>
       </c>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="9" t="s">
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="66"/>
+      <c r="B10" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="52" t="s">
+      <c r="D10" s="4"/>
+      <c r="E10" s="52" t="s">
         <v>368</v>
       </c>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="9" t="s">
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="66"/>
+      <c r="B11" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="4"/>
+      <c r="E11" s="52" t="s">
         <v>369</v>
       </c>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="55"/>
-      <c r="B12" s="56"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="66"/>
+      <c r="B12" s="55"/>
       <c r="C12" s="56"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="56"/>
-    </row>
-    <row r="13" spans="1:5" ht="409.5">
-      <c r="A13" s="9" t="s">
+      <c r="D12" s="56"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="56"/>
+    </row>
+    <row r="13" spans="1:6" ht="200.1" customHeight="1">
+      <c r="A13" s="66"/>
+      <c r="B13" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="E13" s="52" t="s">
+        <v>395</v>
+      </c>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" ht="24">
+      <c r="A14" s="66"/>
+      <c r="B14" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="52" t="s">
+        <v>373</v>
+      </c>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="66"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="56"/>
+    </row>
+    <row r="16" spans="1:6" ht="168">
+      <c r="A16" s="66"/>
+      <c r="B16" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="E16" s="52" t="s">
+        <v>396</v>
+      </c>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" ht="24">
+      <c r="A17" s="66"/>
+      <c r="B17" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E17" s="52" t="s">
+        <v>378</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="66"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="56"/>
+    </row>
+    <row r="19" spans="1:6" ht="168">
+      <c r="A19" s="66"/>
+      <c r="B19" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>396</v>
+      </c>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" ht="24">
+      <c r="A20" s="67"/>
+      <c r="B20" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>378</v>
+      </c>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="55"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="56"/>
+    </row>
+    <row r="22" spans="1:6" ht="200.1" customHeight="1">
+      <c r="A22" s="68" t="s">
+        <v>404</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="52" t="s">
         <v>384</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="D13" s="52" t="s">
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" ht="192">
+      <c r="A23" s="69"/>
+      <c r="B23" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" ht="24">
-      <c r="A14" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="52" t="s">
-        <v>373</v>
-      </c>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="55"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="56"/>
-    </row>
-    <row r="16" spans="1:5" ht="168">
-      <c r="A16" s="9" t="s">
+      <c r="D23" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="E23" s="52" t="s">
+        <v>397</v>
+      </c>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" ht="36">
+      <c r="A24" s="69"/>
+      <c r="B24" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="D16" s="52" t="s">
-        <v>383</v>
-      </c>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" ht="24">
-      <c r="A17" s="9" t="s">
+      <c r="E24" s="52" t="s">
         <v>378</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="D17" s="52" t="s">
-        <v>380</v>
-      </c>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="55"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="56"/>
-    </row>
-    <row r="19" spans="1:5" ht="168">
-      <c r="A19" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="D19" s="52" t="s">
-        <v>383</v>
-      </c>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="24">
-      <c r="A20" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="D20" s="52" t="s">
-        <v>380</v>
-      </c>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="55"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="56"/>
-    </row>
-    <row r="22" spans="1:5" ht="409.5">
-      <c r="A22" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="52" t="s">
-        <v>390</v>
-      </c>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" ht="192">
-      <c r="A23" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="D23" s="52" t="s">
-        <v>381</v>
-      </c>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5" ht="36">
-      <c r="A24" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="D24" s="52" t="s">
-        <v>380</v>
-      </c>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="55"/>
-      <c r="B25" s="56"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="69"/>
+      <c r="B25" s="55"/>
       <c r="C25" s="56"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="56"/>
-    </row>
-    <row r="26" spans="1:5" ht="192">
-      <c r="A26" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="D26" s="52" t="s">
-        <v>382</v>
-      </c>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5" ht="36">
-      <c r="A27" s="9" t="s">
+      <c r="D25" s="56"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="56"/>
+    </row>
+    <row r="26" spans="1:6" ht="192">
+      <c r="A26" s="69"/>
+      <c r="B26" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="E26" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="D27" s="52" t="s">
-        <v>380</v>
-      </c>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" ht="36">
+      <c r="A27" s="70"/>
+      <c r="B27" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E27" s="52" t="s">
+        <v>378</v>
+      </c>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="55"/>
-      <c r="B28" s="56"/>
+      <c r="B28" s="55"/>
       <c r="C28" s="56"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="56"/>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="D28" s="56"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="56"/>
+    </row>
+    <row r="29" spans="1:6" ht="200.1" customHeight="1">
       <c r="A29" s="9"/>
-      <c r="B29" s="4"/>
+      <c r="B29" s="9" t="s">
+        <v>400</v>
+      </c>
       <c r="C29" s="4"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="D29" s="9"/>
+      <c r="E29" s="52" t="s">
+        <v>401</v>
+      </c>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6" ht="168">
       <c r="A30" s="9"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="B30" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="E30" s="52" t="s">
+        <v>402</v>
+      </c>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6" ht="36">
       <c r="A31" s="9"/>
-      <c r="B31" s="4"/>
+      <c r="B31" s="9" t="s">
+        <v>406</v>
+      </c>
       <c r="C31" s="4"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="4"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="9"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="4"/>
+      <c r="D31" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E31" s="52" t="s">
+        <v>378</v>
+      </c>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="55"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="56"/>
+    </row>
+    <row r="33" spans="1:6" ht="168">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="E33" s="52" t="s">
+        <v>402</v>
+      </c>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6" ht="36">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E34" s="52" t="s">
+        <v>378</v>
+      </c>
+      <c r="F34" s="4"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A20"/>
+    <mergeCell ref="A22:A27"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6575,12 +6803,12 @@
     </row>
     <row r="2" spans="1:5" ht="243" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="9"/>
       <c r="D2" s="58" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="E2" s="4"/>
     </row>
@@ -6593,12 +6821,12 @@
     </row>
     <row r="4" spans="1:5" ht="200.1" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9"/>
       <c r="D4" s="58" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="E4" s="4"/>
     </row>
